--- a/business_forms/036_incomplete_work_items_report_form--business_forms.xlsx
+++ b/business_forms/036_incomplete_work_items_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>report_date_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reported Date</t>
+          <t>Reported Date (2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tool_status</t>
+          <t>tool_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tool Status</t>
+          <t>Tool Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tool_type</t>
+          <t>tool_type_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tool Type</t>
+          <t>Tool Type 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>report_date_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Report Date 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tool_status_choices</t>
+          <t>tool_status_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tool_status_choices</t>
+          <t>tool_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tool_type_choices</t>
+          <t>tool_type_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tool_type_choices</t>
+          <t>tool_type_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
